--- a/Stats Sheet/Round Gaps/Abstraction.xlsx
+++ b/Stats Sheet/Round Gaps/Abstraction.xlsx
@@ -70,6 +70,9 @@
     <x:t>18</x:t>
   </x:si>
   <x:si>
+    <x:t>19</x:t>
+  </x:si>
+  <x:si>
     <x:t>_Glen</x:t>
   </x:si>
   <x:si>
@@ -157,6 +160,9 @@
     <x:t>1107</x:t>
   </x:si>
   <x:si>
+    <x:t>997</x:t>
+  </x:si>
+  <x:si>
     <x:t>chloesad</x:t>
   </x:si>
   <x:si>
@@ -190,6 +196,9 @@
     <x:t>MajorWoof</x:t>
   </x:si>
   <x:si>
+    <x:t>1297</x:t>
+  </x:si>
+  <x:si>
     <x:t>MercuryParadox</x:t>
   </x:si>
   <x:si>
@@ -214,6 +223,9 @@
     <x:t>300</x:t>
   </x:si>
   <x:si>
+    <x:t>510</x:t>
+  </x:si>
+  <x:si>
     <x:t>SD_UHC</x:t>
   </x:si>
   <x:si>
@@ -328,6 +340,9 @@
     <x:t>JustNolan</x:t>
   </x:si>
   <x:si>
+    <x:t>2730</x:t>
+  </x:si>
+  <x:si>
     <x:t>MistaUnicorn</x:t>
   </x:si>
   <x:si>
@@ -409,6 +424,9 @@
     <x:t>996</x:t>
   </x:si>
   <x:si>
+    <x:t>301</x:t>
+  </x:si>
+  <x:si>
     <x:t>Fra49</x:t>
   </x:si>
   <x:si>
@@ -629,6 +647,24 @@
   </x:si>
   <x:si>
     <x:t>Psykl0ne</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Andronify</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Fensua</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxEvasion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Maxwellfifty</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Plushy33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thimburrr</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -987,10 +1023,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:V130"/>
+  <x:dimension ref="A1:W136"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:22" s="1" customFormat="1">
+    <x:row r="1" spans="1:23" s="1" customFormat="1">
       <x:c r="E1" s="1">
         <x:v>43092</x:v>
       </x:c>
@@ -1045,8 +1081,11 @@
       <x:c r="V1" s="1">
         <x:v>45849</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:22">
+      <x:c r="W1" s="1">
+        <x:v>46115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:23">
       <x:c r="F2" s="0">
         <x:v>187</x:v>
       </x:c>
@@ -1098,8 +1137,11 @@
       <x:c r="V2" s="0">
         <x:v>35</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:22">
+      <x:c r="W2" s="0">
+        <x:v>266</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:23">
       <x:c r="E3" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -1154,13 +1196,16 @@
       <x:c r="V3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" spans="1:22">
+      <x:c r="W3" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:23">
       <x:c r="A4" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
         <x:v>0</x:v>
@@ -1169,18 +1214,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:22">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:23">
       <x:c r="A5" s="0">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>0</x:v>
@@ -1189,36 +1234,36 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R5" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:22">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:23">
       <x:c r="A6" s="0">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
         <x:v>0</x:v>
@@ -1227,30 +1272,30 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:22">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:23">
       <x:c r="A7" s="0">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>0</x:v>
@@ -1259,166 +1304,172 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N7" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:23">
       <x:c r="A8" s="0">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S8" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="T8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V8" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:22">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="W8" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:23">
       <x:c r="A9" s="0">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P9" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="Q9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V9" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W9" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:23">
       <x:c r="A10" s="0">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>0</x:v>
@@ -1427,30 +1478,30 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:22">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:23">
       <x:c r="A11" s="0">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>0</x:v>
@@ -1459,18 +1510,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N11" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:22">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:23">
       <x:c r="A12" s="0">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>0</x:v>
@@ -1479,36 +1530,36 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N12" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:23">
       <x:c r="A13" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>0</x:v>
@@ -1517,47 +1568,50 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="P13" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:22">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:23">
       <x:c r="A14" s="0">
         <x:v>11</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Q14" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="R14" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W14" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:23">
       <x:c r="A15" s="0">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>0</x:v>
@@ -1566,39 +1620,39 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L15" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N15" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O15" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P15" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:23">
       <x:c r="A16" s="0">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>0</x:v>
@@ -1607,45 +1661,45 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N16" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="P16" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="V16" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:22">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:23">
       <x:c r="A17" s="0">
         <x:v>14</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>0</x:v>
@@ -1654,27 +1708,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="L17" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M17" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O17" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:22">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:23">
       <x:c r="A18" s="0">
         <x:v>15</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>0</x:v>
@@ -1683,65 +1737,68 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:22">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:23">
       <x:c r="A19" s="0">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I19" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J19" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L19" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M19" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N19" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O19" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P19" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W19" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:23">
       <x:c r="A20" s="0">
         <x:v>17</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
         <x:v>0</x:v>
@@ -1750,39 +1807,39 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O20" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="P20" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q20" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R20" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T20" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:22">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:23">
       <x:c r="A21" s="0">
         <x:v>18</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
         <x:v>0</x:v>
@@ -1791,30 +1848,30 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I21" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L21" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M21" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:23">
       <x:c r="A22" s="0">
         <x:v>19</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
         <x:v>0</x:v>
@@ -1823,74 +1880,77 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I22" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="L22" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:22">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:23">
       <x:c r="A23" s="0">
         <x:v>20</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P23" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="R23" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="T23" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:22">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="W23" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:23">
       <x:c r="A24" s="0">
         <x:v>21</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
         <x:v>0</x:v>
@@ -1899,30 +1959,30 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="I24" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L24" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M24" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:23">
       <x:c r="A25" s="0">
         <x:v>22</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
         <x:v>0</x:v>
@@ -1931,51 +1991,51 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H25" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I25" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J25" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L25" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="M25" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N25" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O25" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P25" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q25" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R25" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:23">
       <x:c r="A26" s="0">
         <x:v>23</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
         <x:v>0</x:v>
@@ -1984,27 +2044,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="L26" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M26" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N26" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:23">
       <x:c r="A27" s="0">
         <x:v>24</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
         <x:v>0</x:v>
@@ -2013,39 +2073,39 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I27" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J27" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M27" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="N27" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:23">
       <x:c r="A28" s="0">
         <x:v>25</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
         <x:v>0</x:v>
@@ -2054,15 +2114,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:23">
       <x:c r="A29" s="0">
         <x:v>26</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
         <x:v>0</x:v>
@@ -2071,24 +2131,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="I29" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:23">
       <x:c r="A30" s="0">
         <x:v>27</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
         <x:v>0</x:v>
@@ -2097,33 +2157,33 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J30" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L30" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:23">
       <x:c r="A31" s="0">
         <x:v>28</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
         <x:v>0</x:v>
@@ -2132,21 +2192,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L31" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:22">
+        <x:v>79</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:23">
       <x:c r="A32" s="0">
         <x:v>29</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
         <x:v>1</x:v>
@@ -2155,18 +2215,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L32" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:22">
+        <x:v>79</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:23">
       <x:c r="A33" s="0">
         <x:v>30</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
         <x:v>1</x:v>
@@ -2175,92 +2235,95 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H33" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I33" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J33" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M33" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="O33" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="Q33" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:22">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:23">
       <x:c r="A34" s="0">
         <x:v>31</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H34" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="I34" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J34" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L34" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="M34" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N34" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P34" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="R34" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="S34" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T34" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U34" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V34" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W34" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:23">
       <x:c r="A35" s="0">
         <x:v>32</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
         <x:v>1</x:v>
@@ -2269,24 +2332,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H35" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M35" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:22">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:23">
       <x:c r="A36" s="0">
         <x:v>33</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
         <x:v>1</x:v>
@@ -2295,48 +2358,48 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H36" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I36" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J36" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K36" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N36" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="O36" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P36" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q36" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T36" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="V36" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:22">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:23">
       <x:c r="A37" s="0">
         <x:v>34</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
         <x:v>1</x:v>
@@ -2345,21 +2408,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I37" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="N37" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:22">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:23">
       <x:c r="A38" s="0">
         <x:v>35</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
         <x:v>1</x:v>
@@ -2368,109 +2431,115 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J38" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="L38" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="P38" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:22">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:23">
       <x:c r="A39" s="0">
         <x:v>36</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O39" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="P39" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R39" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="T39" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="V39" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:22">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="W39" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:23">
       <x:c r="A40" s="0">
         <x:v>37</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H40" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I40" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J40" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L40" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N40" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="P40" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="R40" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="S40" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U40" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="V40" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W40" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:23">
       <x:c r="A41" s="0">
         <x:v>38</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
         <x:v>1</x:v>
@@ -2479,15 +2548,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:23">
       <x:c r="A42" s="0">
         <x:v>39</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
         <x:v>2</x:v>
@@ -2496,21 +2565,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G42" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H42" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I42" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:23">
       <x:c r="A43" s="0">
         <x:v>40</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
         <x:v>2</x:v>
@@ -2519,18 +2588,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G43" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H43" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:23">
       <x:c r="A44" s="0">
         <x:v>41</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
         <x:v>2</x:v>
@@ -2539,50 +2608,53 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G44" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H44" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I44" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J44" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K44" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P44" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:22">
+        <x:v>101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:23">
       <x:c r="A45" s="0">
         <x:v>42</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G45" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P45" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:22">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="W45" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:23">
       <x:c r="A46" s="0">
         <x:v>43</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
         <x:v>2</x:v>
@@ -2591,18 +2663,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G46" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H46" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:23">
       <x:c r="A47" s="0">
         <x:v>44</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
         <x:v>2</x:v>
@@ -2611,51 +2683,51 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="G47" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H47" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J47" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K47" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L47" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M47" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N47" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O47" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P47" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R47" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="S47" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U47" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="V47" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:23">
       <x:c r="A48" s="0">
         <x:v>45</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
         <x:v>2</x:v>
@@ -2664,59 +2736,62 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G48" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H48" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I48" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J48" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K48" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L48" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M48" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N48" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O48" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P48" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:23">
       <x:c r="A49" s="0">
         <x:v>46</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G49" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W49" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:23">
       <x:c r="A50" s="0">
         <x:v>47</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
         <x:v>2</x:v>
@@ -2725,18 +2800,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G50" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J50" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:22">
+        <x:v>110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:23">
       <x:c r="A51" s="0">
         <x:v>48</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
         <x:v>2</x:v>
@@ -2745,39 +2820,39 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="G51" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H51" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I51" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J51" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K51" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N51" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="P51" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="Q51" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R51" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:23">
       <x:c r="A52" s="0">
         <x:v>49</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
         <x:v>2</x:v>
@@ -2786,36 +2861,36 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="G52" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H52" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I52" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K52" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L52" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P52" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="R52" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="U52" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:22">
+        <x:v>113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:23">
       <x:c r="A53" s="0">
         <x:v>50</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
         <x:v>2</x:v>
@@ -2824,27 +2899,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G53" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H53" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I53" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J53" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K53" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:23">
       <x:c r="A54" s="0">
         <x:v>51</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
         <x:v>3</x:v>
@@ -2853,136 +2928,142 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="H54" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K54" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="L54" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M54" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N54" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P54" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:22">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:23">
       <x:c r="A55" s="0">
         <x:v>52</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H55" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I55" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J55" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L55" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="M55" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N55" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O55" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P55" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q55" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R55" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T55" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="U55" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V55" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W55" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:23">
       <x:c r="A56" s="0">
         <x:v>53</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D56" s="0">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H56" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I56" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J56" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K56" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L56" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M56" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O56" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="P56" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q56" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R56" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T56" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="U56" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V56" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W56" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:23">
       <x:c r="A57" s="0">
         <x:v>54</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
         <x:v>3</x:v>
@@ -2991,18 +3072,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H57" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I57" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:23">
       <x:c r="A58" s="0">
         <x:v>55</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
         <x:v>3</x:v>
@@ -3011,21 +3092,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H58" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q58" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="U58" s="0" t="s">
-        <x:v>117</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:22">
+        <x:v>122</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:23">
       <x:c r="A59" s="0">
         <x:v>56</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
         <x:v>3</x:v>
@@ -3034,15 +3115,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H59" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:23">
       <x:c r="A60" s="0">
         <x:v>57</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
         <x:v>3</x:v>
@@ -3051,15 +3132,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H60" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:23">
       <x:c r="A61" s="0">
         <x:v>58</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
         <x:v>3</x:v>
@@ -3068,30 +3149,30 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="H61" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I61" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J61" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K61" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L61" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R61" s="0" t="s">
-        <x:v>121</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" spans="1:22">
+        <x:v>126</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:23">
       <x:c r="A62" s="0">
         <x:v>59</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
         <x:v>3</x:v>
@@ -3100,21 +3181,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H62" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I62" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q62" s="0" t="s">
-        <x:v>123</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" spans="1:22">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:23">
       <x:c r="A63" s="0">
         <x:v>60</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
         <x:v>3</x:v>
@@ -3123,15 +3204,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H63" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:23">
       <x:c r="A64" s="0">
         <x:v>61</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
         <x:v>3</x:v>
@@ -3140,33 +3221,33 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="H64" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I64" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J64" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K64" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L64" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N64" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O64" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:23">
       <x:c r="A65" s="0">
         <x:v>62</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
         <x:v>3</x:v>
@@ -3175,65 +3256,68 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="H65" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I65" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J65" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N65" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="O65" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P65" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T65" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="V65" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" spans="1:22">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:23">
       <x:c r="A66" s="0">
         <x:v>63</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D66" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I66" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K66" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L66" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P66" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="U66" s="0" t="s">
-        <x:v>130</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" spans="1:22">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="W66" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:23">
       <x:c r="A67" s="0">
         <x:v>64</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
         <x:v>4</x:v>
@@ -3242,95 +3326,98 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I67" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K67" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L67" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M67" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N67" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O67" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P67" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q67" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T67" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="U67" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:23">
       <x:c r="A68" s="0">
         <x:v>65</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D68" s="0">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I68" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J68" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K68" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L68" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M68" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N68" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O68" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P68" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q68" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R68" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T68" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="U68" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V68" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W68" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:23">
       <x:c r="A69" s="0">
         <x:v>66</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
         <x:v>4</x:v>
@@ -3339,24 +3426,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I69" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N69" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="O69" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P69" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:23">
       <x:c r="A70" s="0">
         <x:v>67</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
         <x:v>4</x:v>
@@ -3365,15 +3452,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I70" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="71" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:23">
       <x:c r="A71" s="0">
         <x:v>68</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
         <x:v>4</x:v>
@@ -3382,30 +3469,30 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I71" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J71" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K71" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L71" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M71" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q71" s="0" t="s">
-        <x:v>136</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72" spans="1:22">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:23">
       <x:c r="A72" s="0">
         <x:v>69</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
         <x:v>4</x:v>
@@ -3414,18 +3501,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I72" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L72" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" spans="1:22">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:23">
       <x:c r="A73" s="0">
         <x:v>70</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
         <x:v>4</x:v>
@@ -3434,27 +3521,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I73" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J73" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P73" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="Q73" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R73" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:23">
       <x:c r="A74" s="0">
         <x:v>71</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
         <x:v>4</x:v>
@@ -3463,39 +3550,39 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="I74" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J74" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K74" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L74" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M74" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N74" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O74" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S74" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="T74" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:23">
       <x:c r="A75" s="0">
         <x:v>72</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
         <x:v>4</x:v>
@@ -3504,27 +3591,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I75" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K75" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L75" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M75" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S75" s="0" t="s">
-        <x:v>143</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76" spans="1:22">
+        <x:v>149</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:23">
       <x:c r="A76" s="0">
         <x:v>73</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
         <x:v>5</x:v>
@@ -3533,27 +3620,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J76" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K76" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L76" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N76" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q76" s="0" t="s">
-        <x:v>145</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="77" spans="1:22">
+        <x:v>151</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:23">
       <x:c r="A77" s="0">
         <x:v>74</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
         <x:v>5</x:v>
@@ -3562,18 +3649,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="J77" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K77" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="78" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:23">
       <x:c r="A78" s="0">
         <x:v>75</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
         <x:v>5</x:v>
@@ -3582,27 +3669,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J78" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K78" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M78" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="N78" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V78" s="0" t="s">
-        <x:v>148</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79" spans="1:22">
+        <x:v>154</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:23">
       <x:c r="A79" s="0">
         <x:v>76</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
         <x:v>5</x:v>
@@ -3611,27 +3698,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J79" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K79" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N79" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="O79" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P79" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:23">
       <x:c r="A80" s="0">
         <x:v>77</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
         <x:v>5</x:v>
@@ -3640,15 +3727,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J80" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:23">
       <x:c r="A81" s="0">
         <x:v>78</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
         <x:v>5</x:v>
@@ -3657,24 +3744,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="J81" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L81" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="R81" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="T81" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82" spans="1:22">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:23">
       <x:c r="A82" s="0">
         <x:v>79</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
         <x:v>6</x:v>
@@ -3683,18 +3770,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="K82" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L82" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="83" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:23">
       <x:c r="A83" s="0">
         <x:v>80</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
         <x:v>6</x:v>
@@ -3703,21 +3790,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="K83" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L83" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M83" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:23">
       <x:c r="A84" s="0">
         <x:v>81</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
         <x:v>6</x:v>
@@ -3726,18 +3813,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="K84" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L84" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="85" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:23">
       <x:c r="A85" s="0">
         <x:v>82</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
         <x:v>6</x:v>
@@ -3746,15 +3833,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K85" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="86" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:23">
       <x:c r="A86" s="0">
         <x:v>83</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
         <x:v>6</x:v>
@@ -3763,27 +3850,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="K86" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L86" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M86" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N86" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O86" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="87" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:23">
       <x:c r="A87" s="0">
         <x:v>84</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
         <x:v>6</x:v>
@@ -3792,18 +3879,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="K87" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L87" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="88" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:23">
       <x:c r="A88" s="0">
         <x:v>85</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
         <x:v>7</x:v>
@@ -3812,24 +3899,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="L88" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M88" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N88" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R88" s="0" t="s">
-        <x:v>159</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="89" spans="1:22">
+        <x:v>165</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:23">
       <x:c r="A89" s="0">
         <x:v>86</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
         <x:v>7</x:v>
@@ -3838,15 +3925,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L89" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="90" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:23">
       <x:c r="A90" s="0">
         <x:v>87</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
         <x:v>7</x:v>
@@ -3855,15 +3942,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L90" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:23">
       <x:c r="A91" s="0">
         <x:v>88</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
         <x:v>7</x:v>
@@ -3872,18 +3959,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="L91" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N91" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="92" spans="1:22">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:23">
       <x:c r="A92" s="0">
         <x:v>89</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
         <x:v>8</x:v>
@@ -3892,24 +3979,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="M92" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O92" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="P92" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R92" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="93" spans="1:22">
+        <x:v>68</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:23">
       <x:c r="A93" s="0">
         <x:v>90</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
         <x:v>8</x:v>
@@ -3918,65 +4005,68 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="M93" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N93" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O93" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R93" s="0" t="s">
-        <x:v>165</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="94" spans="1:22">
+        <x:v>171</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:23">
       <x:c r="A94" s="0">
         <x:v>91</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D94" s="0">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="M94" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N94" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O94" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P94" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R94" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="S94" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T94" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U94" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V94" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W94" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:23">
       <x:c r="A95" s="0">
         <x:v>92</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
         <x:v>8</x:v>
@@ -3985,21 +4075,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="M95" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N95" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U95" s="0" t="s">
-        <x:v>168</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="96" spans="1:22">
+        <x:v>174</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:23">
       <x:c r="A96" s="0">
         <x:v>93</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
         <x:v>8</x:v>
@@ -4008,30 +4098,30 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="M96" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N96" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q96" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="R96" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S96" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U96" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="97" spans="1:22">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:23">
       <x:c r="A97" s="0">
         <x:v>94</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
         <x:v>9</x:v>
@@ -4040,109 +4130,115 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="N97" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O97" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P97" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T97" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="U97" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V97" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:23">
       <x:c r="A98" s="0">
         <x:v>95</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D98" s="0">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="N98" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O98" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P98" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q98" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R98" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S98" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T98" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U98" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V98" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="99" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W98" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:23">
       <x:c r="A99" s="0">
         <x:v>96</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D99" s="0">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="N99" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O99" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P99" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q99" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R99" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S99" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T99" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U99" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="100" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W99" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:23">
       <x:c r="A100" s="0">
         <x:v>97</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
         <x:v>9</x:v>
@@ -4151,24 +4247,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="N100" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q100" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="S100" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="U100" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="101" spans="1:22">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:23">
       <x:c r="A101" s="0">
         <x:v>98</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
         <x:v>9</x:v>
@@ -4177,15 +4273,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="N101" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="102" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:23">
       <x:c r="A102" s="0">
         <x:v>99</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
         <x:v>9</x:v>
@@ -4194,15 +4290,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="N102" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="103" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:23">
       <x:c r="A103" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
         <x:v>10</x:v>
@@ -4211,47 +4307,50 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="O103" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P103" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="104" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:23">
       <x:c r="A104" s="0">
         <x:v>101</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D104" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="O104" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P104" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T104" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="U104" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V104" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="105" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W104" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:23">
       <x:c r="A105" s="0">
         <x:v>102</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
         <x:v>10</x:v>
@@ -4260,15 +4359,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="O105" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="106" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:23">
       <x:c r="A106" s="0">
         <x:v>103</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
         <x:v>10</x:v>
@@ -4277,38 +4376,41 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="O106" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="107" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" spans="1:23">
       <x:c r="A107" s="0">
         <x:v>104</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D107" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="O107" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P107" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R107" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="108" spans="1:22">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="W107" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:23">
       <x:c r="A108" s="0">
         <x:v>105</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
         <x:v>10</x:v>
@@ -4317,36 +4419,36 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="O108" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P108" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q108" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R108" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S108" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T108" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U108" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V108" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="109" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:23">
       <x:c r="A109" s="0">
         <x:v>106</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
         <x:v>10</x:v>
@@ -4355,21 +4457,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="O109" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P109" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R109" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="110" spans="1:22">
+        <x:v>68</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:23">
       <x:c r="A110" s="0">
         <x:v>107</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
         <x:v>10</x:v>
@@ -4378,30 +4480,30 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="O110" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P110" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q110" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R110" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S110" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U110" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="111" spans="1:22">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:23">
       <x:c r="A111" s="0">
         <x:v>108</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
         <x:v>11</x:v>
@@ -4410,18 +4512,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="P111" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q111" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="112" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" spans="1:23">
       <x:c r="A112" s="0">
         <x:v>109</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
         <x:v>11</x:v>
@@ -4430,30 +4532,30 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="P112" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q112" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R112" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S112" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T112" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U112" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="113" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" spans="1:23">
       <x:c r="A113" s="0">
         <x:v>110</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
         <x:v>11</x:v>
@@ -4462,33 +4564,33 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="P113" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q113" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R113" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S113" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T113" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U113" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V113" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="114" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" spans="1:23">
       <x:c r="A114" s="0">
         <x:v>111</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
         <x:v>11</x:v>
@@ -4497,15 +4599,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="P114" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="115" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:23">
       <x:c r="A115" s="0">
         <x:v>112</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
         <x:v>11</x:v>
@@ -4514,24 +4616,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="P115" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q115" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R115" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S115" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="116" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:23">
       <x:c r="A116" s="0">
         <x:v>113</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
         <x:v>11</x:v>
@@ -4540,15 +4642,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="P116" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="117" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:23">
       <x:c r="A117" s="0">
         <x:v>114</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
         <x:v>11</x:v>
@@ -4557,44 +4659,47 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="P117" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="118" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" spans="1:23">
       <x:c r="A118" s="0">
         <x:v>115</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D118" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="Q118" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R118" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S118" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U118" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="V118" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="119" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W118" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" spans="1:23">
       <x:c r="A119" s="0">
         <x:v>116</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
         <x:v>12</x:v>
@@ -4603,24 +4708,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="Q119" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S119" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="U119" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="V119" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="120" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" spans="1:23">
       <x:c r="A120" s="0">
         <x:v>117</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
         <x:v>14</x:v>
@@ -4629,15 +4734,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S120" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="121" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" spans="1:23">
       <x:c r="A121" s="0">
         <x:v>118</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
         <x:v>14</x:v>
@@ -4646,21 +4751,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="S121" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U121" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="V121" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="122" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" spans="1:23">
       <x:c r="A122" s="0">
         <x:v>119</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
         <x:v>15</x:v>
@@ -4669,18 +4774,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="T122" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U122" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="123" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" spans="1:23">
       <x:c r="A123" s="0">
         <x:v>120</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
         <x:v>15</x:v>
@@ -4689,38 +4794,41 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="T123" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V123" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="124" spans="1:22">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" spans="1:23">
       <x:c r="A124" s="0">
         <x:v>121</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D124" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="U124" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V124" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="125" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W124" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" spans="1:23">
       <x:c r="A125" s="0">
         <x:v>122</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
         <x:v>16</x:v>
@@ -4729,18 +4837,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="U125" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V125" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="126" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" spans="1:23">
       <x:c r="A126" s="0">
         <x:v>123</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
         <x:v>16</x:v>
@@ -4749,18 +4857,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="U126" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V126" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="127" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" spans="1:23">
       <x:c r="A127" s="0">
         <x:v>124</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
         <x:v>16</x:v>
@@ -4769,15 +4877,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U127" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="128" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" spans="1:23">
       <x:c r="A128" s="0">
         <x:v>125</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
         <x:v>16</x:v>
@@ -4786,15 +4894,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U128" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="129" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" spans="1:23">
       <x:c r="A129" s="0">
         <x:v>126</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
         <x:v>17</x:v>
@@ -4803,15 +4911,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="V129" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="130" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" spans="1:23">
       <x:c r="A130" s="0">
         <x:v>127</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
         <x:v>17</x:v>
@@ -4820,7 +4928,109 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="V130" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" spans="1:23">
+      <x:c r="A131" s="0">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B131" s="0" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="C131" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D131" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W131" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" spans="1:23">
+      <x:c r="A132" s="0">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="B132" s="0" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="C132" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D132" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W132" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" spans="1:23">
+      <x:c r="A133" s="0">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B133" s="0" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="C133" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D133" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W133" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" spans="1:23">
+      <x:c r="A134" s="0">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B134" s="0" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="C134" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D134" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W134" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" spans="1:23">
+      <x:c r="A135" s="0">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B135" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="C135" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D135" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W135" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" spans="1:23">
+      <x:c r="A136" s="0">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B136" s="0" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="C136" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D136" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W136" s="0" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
